--- a/resources/entity_prefab.xlsx
+++ b/resources/entity_prefab.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="740" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Base" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">Base!#REF!</definedName>
@@ -1362,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20.875" customWidth="1" style="3" min="1" max="1"/>
@@ -4102,6 +4102,29 @@
         <is>
           <t>10070</t>
         </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>10013112016</v>
+      </c>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="26" t="inlineStr">
+        <is>
+          <t>WorldNonPlayer</t>
+        </is>
+      </c>
+      <c r="D108" s="26" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>铁匠老张</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n"/>
+      <c r="H108" s="12" t="n">
+        <v>10071</v>
       </c>
     </row>
   </sheetData>

--- a/resources/entity_prefab.xlsx
+++ b/resources/entity_prefab.xlsx
@@ -992,6 +992,93 @@
 </comments>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>10</col>
+      <colOff>266700</colOff>
+      <row>64</row>
+      <rowOff>133350</rowOff>
+    </from>
+    <to>
+      <col>13</col>
+      <colOff>218824</colOff>
+      <row>73</row>
+      <rowOff>66448</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="图片 3"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="14449425" y="14735175"/>
+          <a:ext cx="2009524" cy="1819048"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>13</col>
+      <colOff>323724</colOff>
+      <row>0</row>
+      <rowOff>790476</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="图片 4"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="15554325" y="0"/>
+          <a:ext cx="1009524" cy="790476"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
@@ -1484,76 +1571,66 @@
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="5">
-      <c r="A5" s="3" t="n">
-        <v>4009</v>
-      </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="A5" s="24" t="n">
+        <v>5023</v>
+      </c>
+      <c r="B5" s="10" t="n"/>
       <c r="C5" s="26" t="inlineStr">
         <is>
           <t>WorldNonPlayer</t>
         </is>
       </c>
       <c r="D5" s="26" t="n">
-        <v>1015</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>铁匠老张</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="12" t="n">
-        <v>3006</v>
+        <v>1012</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="5">
       <c r="A6" s="24" t="n">
-        <v>5023</v>
-      </c>
-      <c r="B6" s="10" t="n"/>
+        <v>8003</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>特效EffectActor专用</t>
+        </is>
+      </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
+          <t>EffectActor</t>
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>1012</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>6</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" s="5">
       <c r="A7" s="24" t="n">
-        <v>8003</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>特效EffectActor专用</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>EffectActor</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>9999</v>
-      </c>
-      <c r="E7" s="10" t="n"/>
-      <c r="G7" s="6" t="n"/>
+        <v>8004</v>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>青龙</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="5">
       <c r="A8" s="24" t="n">
-        <v>8004</v>
+        <v>8005</v>
       </c>
       <c r="B8" s="10" t="n"/>
-      <c r="C8" s="26" t="n"/>
+      <c r="C8" s="10" t="n"/>
       <c r="D8" s="26" t="n"/>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>青龙</t>
+          <t>白虎</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
@@ -1562,14 +1639,14 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="5">
       <c r="A9" s="24" t="n">
-        <v>8005</v>
+        <v>8006</v>
       </c>
       <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
+      <c r="C9" s="26" t="n"/>
       <c r="D9" s="26" t="n"/>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>白虎</t>
+          <t>朱雀</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
@@ -1578,14 +1655,14 @@
     </row>
     <row r="10" ht="16.5" customHeight="1" s="5">
       <c r="A10" s="24" t="n">
-        <v>8006</v>
+        <v>8007</v>
       </c>
       <c r="B10" s="10" t="n"/>
       <c r="C10" s="26" t="n"/>
       <c r="D10" s="26" t="n"/>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>朱雀</t>
+          <t>孙悟空</t>
         </is>
       </c>
       <c r="G10" s="6" t="n">
@@ -1594,69 +1671,62 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" s="5">
       <c r="A11" s="24" t="n">
-        <v>8007</v>
-      </c>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
+        <v>8008</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>洞府入口</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>ResidenceEntryEntity</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>1046</v>
+      </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>孙悟空</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="6" t="n">
-        <v>6</v>
+          <t>洞府入口</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>4005</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="5">
       <c r="A12" s="24" t="n">
-        <v>8008</v>
+        <v>8009</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>洞府入口</t>
+          <t>洞府实例</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>ResidenceEntryEntity</t>
+          <t>ResidenceEntity</t>
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>1046</v>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>洞府入口</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>4005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="5">
       <c r="A13" s="24" t="n">
-        <v>8009</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>洞府实例</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>ResidenceEntity</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6" t="n"/>
+        <v>8010</v>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="5">
       <c r="A14" s="24" t="n">
-        <v>8010</v>
+        <v>8011</v>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="26" t="n"/>
@@ -1667,7 +1737,7 @@
     </row>
     <row r="15" ht="16.5" customHeight="1" s="5">
       <c r="A15" s="24" t="n">
-        <v>8011</v>
+        <v>8012</v>
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="26" t="n"/>
@@ -1678,7 +1748,7 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" s="5">
       <c r="A16" s="24" t="n">
-        <v>8012</v>
+        <v>8013</v>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="26" t="n"/>
@@ -1689,23 +1759,32 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" s="5">
       <c r="A17" s="24" t="n">
-        <v>8013</v>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="G17" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="12" t="n"/>
+        <v>8014</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>擂台npc</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>WorldNonPlayer</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>1012</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>10001</v>
+      </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="5">
       <c r="A18" s="24" t="n">
-        <v>8014</v>
+        <v>8015</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>擂台npc</t>
+          <t>奖励npc</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
@@ -1717,16 +1796,16 @@
         <v>1012</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>10001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="5">
       <c r="A19" s="24" t="n">
-        <v>8015</v>
+        <v>8016</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>奖励npc</t>
+          <t>传送npc</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
@@ -1738,12 +1817,12 @@
         <v>1012</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>10002</v>
+        <v>10003</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="5">
       <c r="A20" s="24" t="n">
-        <v>8016</v>
+        <v>8017</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1759,12 +1838,12 @@
         <v>1012</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>10003</v>
+        <v>10004</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="5">
       <c r="A21" s="24" t="n">
-        <v>8017</v>
+        <v>8018</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1780,12 +1859,12 @@
         <v>1012</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>10004</v>
+        <v>10005</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="5">
       <c r="A22" s="24" t="n">
-        <v>8018</v>
+        <v>8019</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1801,16 +1880,16 @@
         <v>1012</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>10005</v>
+        <v>10006</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="5">
       <c r="A23" s="24" t="n">
-        <v>8019</v>
+        <v>8020</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>传送npc</t>
+          <t>洞府npc-返回大世界</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
@@ -1821,17 +1900,14 @@
       <c r="D23" s="26" t="n">
         <v>1012</v>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>10006</v>
-      </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="5">
       <c r="A24" s="24" t="n">
-        <v>8020</v>
+        <v>8024</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>洞府npc-返回大世界</t>
+          <t>交互测试（不要用）</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
@@ -1842,12 +1918,18 @@
       <c r="D24" s="26" t="n">
         <v>1012</v>
       </c>
-      <c r="E24" s="10" t="n"/>
-      <c r="H24" s="12" t="n"/>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>交互测试</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>10007</v>
+      </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="5">
       <c r="A25" s="24" t="n">
-        <v>8024</v>
+        <v>8025</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1868,12 +1950,12 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>10007</v>
+        <v>10008</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="5">
       <c r="A26" s="24" t="n">
-        <v>8025</v>
+        <v>8026</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1894,12 +1976,12 @@
         </is>
       </c>
       <c r="H26" s="12" t="n">
-        <v>10008</v>
+        <v>10009</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="5">
       <c r="A27" s="24" t="n">
-        <v>8026</v>
+        <v>8027</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1919,140 +2001,131 @@
           <t>交互测试</t>
         </is>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>10009</v>
-      </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="5">
       <c r="A28" s="24" t="n">
-        <v>8027</v>
+        <v>8028</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>交互测试（不要用）</t>
+          <t>候选时的洞府入口</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="n">
-        <v>1012</v>
+          <t>CandidateResidenceEntryEntity</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>22070</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>交互测试</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n"/>
+          <t>洞天福洞（空）</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>4005</v>
+      </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="5">
       <c r="A29" s="24" t="n">
-        <v>8028</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>候选时的洞府入口</t>
+        <v>8029</v>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>选择出生州</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>CandidateResidenceEntryEntity</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>22070</v>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>洞天福洞（空）</t>
+          <t>StateChooseEntity</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>出生州选择</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4005</v>
+        <v>4007</v>
       </c>
       <c r="H29" s="12" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="5">
       <c r="A30" s="24" t="n">
-        <v>8029</v>
-      </c>
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>选择出生州</t>
+        <v>8030</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>洞府入口</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>StateChooseEntity</t>
+          <t>ResidenceWorldEntryEntity</t>
         </is>
       </c>
       <c r="D30" s="26" t="n">
+        <v>1046</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>洞府大世界入口</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" s="5">
+      <c r="A31" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>帮派攻城车（灵兽推车）</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>WorldSiegeCart</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1012</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" s="5">
+      <c r="A32" s="24" t="n">
+        <v>25001001</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>任务战斗测试</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>WorldNonPlayer</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="n">
         <v>1021</v>
       </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>出生州选择</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>4007</v>
-      </c>
-      <c r="H30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="16.5" customHeight="1" s="5">
-      <c r="A31" s="24" t="n">
-        <v>8030</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>洞府入口</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>ResidenceWorldEntryEntity</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="n">
-        <v>1046</v>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>洞府大世界入口</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>4005</v>
-      </c>
-      <c r="G31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" s="5">
-      <c r="A32" s="3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>帮派攻城车（灵兽推车）</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>WorldSiegeCart</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1012</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H32" s="12" t="n"/>
+      <c r="H32" s="12" t="n">
+        <v>10010</v>
+      </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="5">
       <c r="A33" s="24" t="n">
-        <v>25001001</v>
+        <v>25001002</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -2068,16 +2141,16 @@
         <v>1021</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>10010</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="5">
       <c r="A34" s="24" t="n">
-        <v>25001002</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>任务战斗测试</t>
+        <v>35001001</v>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>练气木桩</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
@@ -2086,21 +2159,27 @@
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>1021</v>
-      </c>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="4" t="n"/>
+        <v>1033</v>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>练气木桩</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>4008</v>
+      </c>
       <c r="H34" s="12" t="n">
-        <v>10011</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="5">
       <c r="A35" s="24" t="n">
-        <v>35001001</v>
+        <v>35001002</v>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>练气木桩</t>
+          <t>筑基木桩</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
@@ -2113,23 +2192,23 @@
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>练气木桩</t>
+          <t>筑基木桩</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
         <v>4008</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>10012</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="5">
       <c r="A36" s="24" t="n">
-        <v>35001002</v>
+        <v>35001003</v>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>筑基木桩</t>
+          <t>金丹木桩</t>
         </is>
       </c>
       <c r="C36" s="26" t="inlineStr">
@@ -2142,23 +2221,23 @@
       </c>
       <c r="E36" s="25" t="inlineStr">
         <is>
-          <t>筑基木桩</t>
+          <t>金丹木桩</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
         <v>4008</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="5">
       <c r="A37" s="24" t="n">
-        <v>35001003</v>
+        <v>35001004</v>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>金丹木桩</t>
+          <t>元婴木桩</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
@@ -2171,23 +2250,23 @@
       </c>
       <c r="E37" s="25" t="inlineStr">
         <is>
-          <t>金丹木桩</t>
+          <t>元婴木桩</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
         <v>4008</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>10014</v>
+        <v>10015</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="5">
       <c r="A38" s="24" t="n">
-        <v>35001004</v>
+        <v>35001005</v>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>元婴木桩</t>
+          <t>化神木桩</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
@@ -2200,23 +2279,23 @@
       </c>
       <c r="E38" s="25" t="inlineStr">
         <is>
-          <t>元婴木桩</t>
+          <t>化神木桩</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
         <v>4008</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>10015</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="5">
-      <c r="A39" s="24" t="n">
-        <v>35001005</v>
-      </c>
-      <c r="B39" s="25" t="inlineStr">
-        <is>
-          <t>化神木桩</t>
+      <c r="A39" s="12" t="n">
+        <v>100010000</v>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>获取洞府</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
@@ -2225,27 +2304,27 @@
         </is>
       </c>
       <c r="D39" s="26" t="n">
-        <v>1033</v>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
-        <is>
-          <t>化神木桩</t>
+        <v>1021</v>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>洞府登记师兄</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>10016</v>
+        <v>10017</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="5">
       <c r="A40" s="12" t="n">
-        <v>100010000</v>
+        <v>100010001</v>
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>获取洞府</t>
+          <t>获取分身</t>
         </is>
       </c>
       <c r="C40" s="26" t="inlineStr">
@@ -2258,23 +2337,23 @@
       </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
-          <t>洞府登记师兄</t>
+          <t>分身导师</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>10017</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="5">
       <c r="A41" s="12" t="n">
-        <v>100010001</v>
+        <v>100010002</v>
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>获取分身</t>
+          <t>更换门派</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
@@ -2287,23 +2366,23 @@
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>分身导师</t>
+          <t>更换门派</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>10018</v>
+        <v>10019</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="5">
       <c r="A42" s="12" t="n">
-        <v>100010002</v>
+        <v>100010003</v>
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>更换门派</t>
+          <t>攻城战传送人</t>
         </is>
       </c>
       <c r="C42" s="26" t="inlineStr">
@@ -2316,23 +2395,23 @@
       </c>
       <c r="E42" s="27" t="inlineStr">
         <is>
-          <t>更换门派</t>
+          <t>攻城战传送人</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>10019</v>
+        <v>10032</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="5">
       <c r="A43" s="12" t="n">
-        <v>100010003</v>
+        <v>100010004</v>
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>攻城战传送人</t>
+          <t>帮派任务使</t>
         </is>
       </c>
       <c r="C43" s="26" t="inlineStr">
@@ -2341,27 +2420,27 @@
         </is>
       </c>
       <c r="D43" s="26" t="n">
-        <v>1021</v>
+        <v>1082</v>
       </c>
       <c r="E43" s="27" t="inlineStr">
         <is>
-          <t>攻城战传送人</t>
+          <t>青龙堂总管</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
         <v>4007</v>
       </c>
-      <c r="H43" s="12" t="n">
-        <v>10032</v>
+      <c r="H43" s="15" t="n">
+        <v>10034</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="5">
       <c r="A44" s="12" t="n">
-        <v>100010004</v>
+        <v>100010005</v>
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>帮派任务使</t>
+          <t>帮派资金管理人</t>
         </is>
       </c>
       <c r="C44" s="26" t="inlineStr">
@@ -2370,27 +2449,27 @@
         </is>
       </c>
       <c r="D44" s="26" t="n">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
-          <t>青龙堂总管</t>
+          <t>白虎堂总管</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>10034</v>
+        <v>10035</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="5">
       <c r="A45" s="12" t="n">
-        <v>100010005</v>
+        <v>100010006</v>
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>帮派资金管理人</t>
+          <t>帮派修炼指导人</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
@@ -2399,27 +2478,27 @@
         </is>
       </c>
       <c r="D45" s="26" t="n">
-        <v>1075</v>
+        <v>1085</v>
       </c>
       <c r="E45" s="27" t="inlineStr">
         <is>
-          <t>白虎堂总管</t>
+          <t>朱雀堂总管</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>10035</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="5">
       <c r="A46" s="12" t="n">
-        <v>100010006</v>
+        <v>100010007</v>
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>帮派修炼指导人</t>
+          <t>帮派福利总管</t>
         </is>
       </c>
       <c r="C46" s="26" t="inlineStr">
@@ -2428,27 +2507,27 @@
         </is>
       </c>
       <c r="D46" s="26" t="n">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E46" s="27" t="inlineStr">
         <is>
-          <t>朱雀堂总管</t>
+          <t>玄武堂总管</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>10036</v>
+        <v>10037</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="5">
       <c r="A47" s="12" t="n">
-        <v>100010007</v>
+        <v>100010008</v>
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>帮派福利总管</t>
+          <t>帮派兽栏</t>
         </is>
       </c>
       <c r="C47" s="26" t="inlineStr">
@@ -2457,27 +2536,27 @@
         </is>
       </c>
       <c r="D47" s="26" t="n">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="E47" s="27" t="inlineStr">
         <is>
-          <t>玄武堂总管</t>
+          <t>毕灵翁</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>10037</v>
+        <v>10038</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="5">
       <c r="A48" s="12" t="n">
-        <v>100010008</v>
+        <v>100010009</v>
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>帮派兽栏</t>
+          <t>帮派灵阁</t>
         </is>
       </c>
       <c r="C48" s="26" t="inlineStr">
@@ -2486,27 +2565,27 @@
         </is>
       </c>
       <c r="D48" s="26" t="n">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="E48" s="27" t="inlineStr">
         <is>
-          <t>毕灵翁</t>
+          <t>柳厢儿</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>10038</v>
+        <v>10039</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="5">
       <c r="A49" s="12" t="n">
-        <v>100010009</v>
+        <v>100010010</v>
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>帮派灵阁</t>
+          <t>帮派金库</t>
         </is>
       </c>
       <c r="C49" s="26" t="inlineStr">
@@ -2515,27 +2594,27 @@
         </is>
       </c>
       <c r="D49" s="26" t="n">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="E49" s="27" t="inlineStr">
         <is>
-          <t>柳厢儿</t>
+          <t>金守严</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>10039</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="5">
       <c r="A50" s="12" t="n">
-        <v>100010010</v>
+        <v>100010011</v>
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>帮派金库</t>
+          <t>帮派书院</t>
         </is>
       </c>
       <c r="C50" s="26" t="inlineStr">
@@ -2544,27 +2623,27 @@
         </is>
       </c>
       <c r="D50" s="26" t="n">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
-          <t>金守严</t>
+          <t>顾书同</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>10040</v>
+        <v>10041</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="5">
       <c r="A51" s="12" t="n">
-        <v>100010011</v>
+        <v>100010012</v>
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>帮派书院</t>
+          <t>帮派商店</t>
         </is>
       </c>
       <c r="C51" s="26" t="inlineStr">
@@ -2573,27 +2652,27 @@
         </is>
       </c>
       <c r="D51" s="26" t="n">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
-          <t>顾书同</t>
+          <t>金算盘</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>10041</v>
+        <v>10042</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="5">
       <c r="A52" s="12" t="n">
-        <v>100010012</v>
+        <v>100010013</v>
       </c>
       <c r="B52" s="27" t="inlineStr">
         <is>
-          <t>帮派商店</t>
+          <t>攻城战传送人(战场内)</t>
         </is>
       </c>
       <c r="C52" s="26" t="inlineStr">
@@ -2602,27 +2681,27 @@
         </is>
       </c>
       <c r="D52" s="26" t="n">
-        <v>1080</v>
+        <v>1021</v>
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>金算盘</t>
+          <t>攻城战传送人</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
         <v>4007</v>
       </c>
-      <c r="H52" s="15" t="n">
-        <v>10042</v>
+      <c r="H52" s="12" t="n">
+        <v>10043</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="5">
       <c r="A53" s="12" t="n">
-        <v>100010013</v>
+        <v>100010014</v>
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>攻城战传送人(战场内)</t>
+          <t>攻城战城门1</t>
         </is>
       </c>
       <c r="C53" s="26" t="inlineStr">
@@ -2635,23 +2714,23 @@
       </c>
       <c r="E53" s="27" t="inlineStr">
         <is>
-          <t>攻城战传送人</t>
+          <t>城门</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>10043</v>
+        <v>10044</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="5">
       <c r="A54" s="12" t="n">
-        <v>100010014</v>
+        <v>100010015</v>
       </c>
       <c r="B54" s="27" t="inlineStr">
         <is>
-          <t>攻城战城门1</t>
+          <t>攻城战城门2</t>
         </is>
       </c>
       <c r="C54" s="26" t="inlineStr">
@@ -2671,16 +2750,16 @@
         <v>4007</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>10044</v>
+        <v>10045</v>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="5">
       <c r="A55" s="12" t="n">
-        <v>100010015</v>
+        <v>100010016</v>
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>攻城战城门2</t>
+          <t>攻城战主府</t>
         </is>
       </c>
       <c r="C55" s="26" t="inlineStr">
@@ -2693,23 +2772,23 @@
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>城门</t>
+          <t>主府</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>10045</v>
+        <v>10046</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="5">
       <c r="A56" s="12" t="n">
-        <v>100010016</v>
+        <v>100010017</v>
       </c>
       <c r="B56" s="27" t="inlineStr">
         <is>
-          <t>攻城战主府</t>
+          <t>攻城战图腾-青龙</t>
         </is>
       </c>
       <c r="C56" s="26" t="inlineStr">
@@ -2722,23 +2801,23 @@
       </c>
       <c r="E56" s="27" t="inlineStr">
         <is>
-          <t>主府</t>
+          <t>青龙</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>10046</v>
+        <v>10047</v>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="5">
       <c r="A57" s="12" t="n">
-        <v>100010017</v>
+        <v>100010018</v>
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>攻城战图腾-青龙</t>
+          <t>攻城战图腾-白虎</t>
         </is>
       </c>
       <c r="C57" s="26" t="inlineStr">
@@ -2751,23 +2830,23 @@
       </c>
       <c r="E57" s="27" t="inlineStr">
         <is>
-          <t>青龙</t>
+          <t>白虎</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>10047</v>
+        <v>10048</v>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="5">
       <c r="A58" s="12" t="n">
-        <v>100010018</v>
+        <v>100010019</v>
       </c>
       <c r="B58" s="27" t="inlineStr">
         <is>
-          <t>攻城战图腾-白虎</t>
+          <t>攻城战图腾-朱雀</t>
         </is>
       </c>
       <c r="C58" s="26" t="inlineStr">
@@ -2780,23 +2859,23 @@
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
-          <t>白虎</t>
+          <t>朱雀</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>10048</v>
+        <v>10049</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="5">
       <c r="A59" s="12" t="n">
-        <v>100010019</v>
+        <v>100010020</v>
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>攻城战图腾-朱雀</t>
+          <t>攻城战图腾-玄武</t>
         </is>
       </c>
       <c r="C59" s="26" t="inlineStr">
@@ -2809,23 +2888,23 @@
       </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>朱雀</t>
+          <t>玄武</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>10049</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" s="5">
       <c r="A60" s="12" t="n">
-        <v>100010020</v>
+        <v>100010021</v>
       </c>
       <c r="B60" s="27" t="inlineStr">
         <is>
-          <t>攻城战图腾-玄武</t>
+          <t>攻城巨兽</t>
         </is>
       </c>
       <c r="C60" s="26" t="inlineStr">
@@ -2834,27 +2913,27 @@
         </is>
       </c>
       <c r="D60" s="26" t="n">
-        <v>1021</v>
+        <v>1118</v>
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>玄武</t>
+          <t>攻城巨兽</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>10050</v>
+        <v>10051</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="5">
       <c r="A61" s="12" t="n">
-        <v>100010021</v>
+        <v>100010022</v>
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>攻城巨兽</t>
+          <t>胜利宝箱</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
@@ -2863,27 +2942,27 @@
         </is>
       </c>
       <c r="D61" s="26" t="n">
-        <v>1118</v>
+        <v>1021</v>
       </c>
       <c r="E61" s="27" t="inlineStr">
         <is>
-          <t>攻城巨兽</t>
+          <t>胜利宝箱</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>10051</v>
+        <v>10052</v>
       </c>
     </row>
     <row r="62" ht="16.5" customHeight="1" s="5">
       <c r="A62" s="12" t="n">
-        <v>100010022</v>
+        <v>100010023</v>
       </c>
       <c r="B62" s="27" t="inlineStr">
         <is>
-          <t>胜利宝箱</t>
+          <t>庆贺宝箱</t>
         </is>
       </c>
       <c r="C62" s="26" t="inlineStr">
@@ -2896,23 +2975,23 @@
       </c>
       <c r="E62" s="27" t="inlineStr">
         <is>
-          <t>胜利宝箱</t>
+          <t>庆贺宝箱</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>10052</v>
+        <v>10053</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="5">
       <c r="A63" s="12" t="n">
-        <v>100010023</v>
+        <v>100010024</v>
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>庆贺宝箱</t>
+          <t>帮派聚义厅</t>
         </is>
       </c>
       <c r="C63" s="26" t="inlineStr">
@@ -2921,27 +3000,27 @@
         </is>
       </c>
       <c r="D63" s="26" t="n">
-        <v>1021</v>
+        <v>1078</v>
       </c>
       <c r="E63" s="27" t="inlineStr">
         <is>
-          <t>庆贺宝箱</t>
+          <t>管世方</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>10053</v>
+        <v>10054</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" s="5">
       <c r="A64" s="12" t="n">
-        <v>100010024</v>
+        <v>100010025</v>
       </c>
       <c r="B64" s="27" t="inlineStr">
         <is>
-          <t>帮派聚义厅</t>
+          <t>切换心法</t>
         </is>
       </c>
       <c r="C64" s="26" t="inlineStr">
@@ -2950,27 +3029,27 @@
         </is>
       </c>
       <c r="D64" s="26" t="n">
-        <v>1078</v>
+        <v>1021</v>
       </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
-          <t>管世方</t>
+          <t>切换心法</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>10054</v>
+        <v>10058</v>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" s="5">
       <c r="A65" s="12" t="n">
-        <v>100010025</v>
+        <v>100010026</v>
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>切换心法</t>
+          <t>创建帮派</t>
         </is>
       </c>
       <c r="C65" s="26" t="inlineStr">
@@ -2983,52 +3062,52 @@
       </c>
       <c r="E65" s="27" t="inlineStr">
         <is>
-          <t>切换心法</t>
+          <t>宗门登记</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>10058</v>
+        <v>10059</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="5">
-      <c r="A66" s="12" t="n">
-        <v>100010026</v>
-      </c>
-      <c r="B66" s="27" t="inlineStr">
-        <is>
-          <t>创建帮派</t>
+      <c r="A66" s="24" t="n">
+        <v>100011000</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
         </is>
       </c>
       <c r="C66" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
+          <t>WorldInteractiveObject</t>
         </is>
       </c>
       <c r="D66" s="26" t="n">
-        <v>1021</v>
-      </c>
-      <c r="E66" s="27" t="inlineStr">
-        <is>
-          <t>宗门登记</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="n">
-        <v>4007</v>
+        <v>1031</v>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>4006</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>10059</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="5">
       <c r="A67" s="24" t="n">
-        <v>100011000</v>
+        <v>100011001</v>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>低级灵脉</t>
+          <t>中级灵脉</t>
         </is>
       </c>
       <c r="C67" s="26" t="inlineStr">
@@ -3041,23 +3120,23 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>低级灵脉</t>
+          <t>中级灵脉</t>
         </is>
       </c>
       <c r="F67" s="6" t="n">
         <v>4006</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>10020</v>
+        <v>10021</v>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1" s="5">
       <c r="A68" s="24" t="n">
-        <v>100011001</v>
+        <v>100011002</v>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>中级灵脉</t>
+          <t>高级灵脉</t>
         </is>
       </c>
       <c r="C68" s="26" t="inlineStr">
@@ -3070,23 +3149,23 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>中级灵脉</t>
+          <t>高级灵脉</t>
         </is>
       </c>
       <c r="F68" s="6" t="n">
         <v>4006</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>10021</v>
+        <v>10022</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="5">
       <c r="A69" s="24" t="n">
-        <v>100011002</v>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>高级灵脉</t>
+        <v>100081000</v>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>洞府出口</t>
         </is>
       </c>
       <c r="C69" s="26" t="inlineStr">
@@ -3095,27 +3174,23 @@
         </is>
       </c>
       <c r="D69" s="26" t="n">
-        <v>1031</v>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>高级灵脉</t>
-        </is>
-      </c>
+        <v>1030</v>
+      </c>
+      <c r="E69" s="13" t="n"/>
       <c r="F69" s="6" t="n">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>10022</v>
+        <v>10023</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="5">
       <c r="A70" s="24" t="n">
-        <v>100081000</v>
+        <v>100081001</v>
       </c>
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>洞府出口</t>
+          <t>洞府传送阵</t>
         </is>
       </c>
       <c r="C70" s="26" t="inlineStr">
@@ -3127,16 +3202,16 @@
         <v>1030</v>
       </c>
       <c r="E70" s="13" t="n"/>
-      <c r="F70" s="6" t="n">
-        <v>4005</v>
+      <c r="F70" s="4" t="n">
+        <v>4007</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>10023</v>
+        <v>10024</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="5">
       <c r="A71" s="24" t="n">
-        <v>100081001</v>
+        <v>100081002</v>
       </c>
       <c r="B71" s="25" t="inlineStr">
         <is>
@@ -3156,95 +3231,99 @@
         <v>4007</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>10024</v>
+        <v>10025</v>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="5">
-      <c r="A72" s="24" t="n">
-        <v>100081002</v>
-      </c>
-      <c r="B72" s="25" t="inlineStr">
-        <is>
-          <t>洞府传送阵</t>
+      <c r="A72" s="12" t="n">
+        <v>100090001</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>灵兽抽奖</t>
         </is>
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>WorldInteractiveObject</t>
-        </is>
-      </c>
-      <c r="D72" s="26" t="n">
-        <v>1030</v>
-      </c>
-      <c r="E72" s="13" t="n"/>
+          <t>WorldNonPlayer</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>灵兽抽奖</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>10025</v>
+        <v>10026</v>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="5">
-      <c r="A73" s="12" t="n">
-        <v>100090001</v>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>灵兽抽奖</t>
+      <c r="A73" s="24" t="n">
+        <v>100181000</v>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>洞府出口</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="n">
-        <v>1012</v>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>灵兽抽奖</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="n">
+          <t>WorldInteractiveObject</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="6" t="n">
+        <v>4005</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>10023</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" customHeight="1" s="5">
+      <c r="A74" s="3" t="n">
+        <v>100191000</v>
+      </c>
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>城市土地</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>WorldNonPlayer</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E74" s="27" t="inlineStr">
+        <is>
+          <t>城市土地</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="n">
         <v>4007</v>
       </c>
-      <c r="H73" s="12" t="n">
-        <v>10026</v>
-      </c>
-    </row>
-    <row r="74" ht="16.5" customHeight="1" s="5">
-      <c r="A74" s="24" t="n">
-        <v>100181000</v>
-      </c>
-      <c r="B74" s="25" t="inlineStr">
-        <is>
-          <t>洞府出口</t>
-        </is>
-      </c>
-      <c r="C74" s="26" t="inlineStr">
-        <is>
-          <t>WorldInteractiveObject</t>
-        </is>
-      </c>
-      <c r="D74" s="26" t="n">
-        <v>1030</v>
-      </c>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="6" t="n">
-        <v>4005</v>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>10023</v>
+      <c r="H74" s="6" t="n">
+        <v>10060</v>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="5">
       <c r="A75" s="3" t="n">
-        <v>100191000</v>
-      </c>
-      <c r="B75" s="25" t="inlineStr">
-        <is>
-          <t>城市土地</t>
+        <v>100201001</v>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>切换心法</t>
         </is>
       </c>
       <c r="C75" s="26" t="inlineStr">
@@ -3257,23 +3336,23 @@
       </c>
       <c r="E75" s="27" t="inlineStr">
         <is>
-          <t>城市土地</t>
+          <t>切换心法</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
         <v>4007</v>
       </c>
-      <c r="H75" s="6" t="n">
-        <v>10060</v>
+      <c r="H75" s="12" t="n">
+        <v>10058</v>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="5">
       <c r="A76" s="3" t="n">
-        <v>100201001</v>
+        <v>100201002</v>
       </c>
       <c r="B76" s="27" t="inlineStr">
         <is>
-          <t>切换心法</t>
+          <t>更换门派</t>
         </is>
       </c>
       <c r="C76" s="26" t="inlineStr">
@@ -3286,23 +3365,23 @@
       </c>
       <c r="E76" s="27" t="inlineStr">
         <is>
-          <t>切换心法</t>
+          <t>更换门派</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>10058</v>
+        <v>10019</v>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="5">
       <c r="A77" s="3" t="n">
-        <v>100201002</v>
+        <v>100201003</v>
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>更换门派</t>
+          <t>获取分身</t>
         </is>
       </c>
       <c r="C77" s="26" t="inlineStr">
@@ -3315,23 +3394,23 @@
       </c>
       <c r="E77" s="27" t="inlineStr">
         <is>
-          <t>更换门派</t>
+          <t>分身导师</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>10019</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="5">
       <c r="A78" s="3" t="n">
-        <v>100201003</v>
+        <v>100201004</v>
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>获取分身</t>
+          <t>获取洞府</t>
         </is>
       </c>
       <c r="C78" s="26" t="inlineStr">
@@ -3344,23 +3423,23 @@
       </c>
       <c r="E78" s="27" t="inlineStr">
         <is>
-          <t>分身导师</t>
+          <t>洞府登记师兄</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>10018</v>
+        <v>10061</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="5">
       <c r="A79" s="3" t="n">
-        <v>100201004</v>
+        <v>100201005</v>
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>获取洞府</t>
+          <t>创建帮派</t>
         </is>
       </c>
       <c r="C79" s="26" t="inlineStr">
@@ -3373,28 +3452,28 @@
       </c>
       <c r="E79" s="27" t="inlineStr">
         <is>
-          <t>洞府登记师兄</t>
+          <t>宗门登记</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
         <v>4007</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>10061</v>
+        <v>10059</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1" s="5">
       <c r="A80" s="3" t="n">
-        <v>100201005</v>
+        <v>100201006</v>
       </c>
       <c r="B80" s="27" t="inlineStr">
         <is>
-          <t>创建帮派</t>
+          <t>真·洞府接引（失效）</t>
         </is>
       </c>
       <c r="C80" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
+          <t>StateChooseEntity</t>
         </is>
       </c>
       <c r="D80" s="26" t="n">
@@ -3402,50 +3481,50 @@
       </c>
       <c r="E80" s="27" t="inlineStr">
         <is>
-          <t>宗门登记</t>
+          <t>真洞府</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
         <v>4007</v>
       </c>
-      <c r="H80" s="12" t="n">
-        <v>10059</v>
-      </c>
+      <c r="H80" s="12" t="n"/>
     </row>
     <row r="81" ht="16.5" customHeight="1" s="5">
       <c r="A81" s="3" t="n">
-        <v>100201006</v>
-      </c>
-      <c r="B81" s="27" t="inlineStr">
-        <is>
-          <t>真·洞府接引（失效）</t>
+        <v>100201007</v>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>练气木桩</t>
         </is>
       </c>
       <c r="C81" s="26" t="inlineStr">
         <is>
-          <t>StateChooseEntity</t>
+          <t>WorldNonPlayer</t>
         </is>
       </c>
       <c r="D81" s="26" t="n">
-        <v>1021</v>
-      </c>
-      <c r="E81" s="27" t="inlineStr">
-        <is>
-          <t>真洞府</t>
+        <v>1033</v>
+      </c>
+      <c r="E81" s="25" t="inlineStr">
+        <is>
+          <t>练气木桩</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>4007</v>
-      </c>
-      <c r="H81" s="12" t="n"/>
+        <v>4008</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>10012</v>
+      </c>
     </row>
     <row r="82" ht="16.5" customHeight="1" s="5">
       <c r="A82" s="3" t="n">
-        <v>100201007</v>
+        <v>100201008</v>
       </c>
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>练气木桩</t>
+          <t>筑基木桩</t>
         </is>
       </c>
       <c r="C82" s="26" t="inlineStr">
@@ -3458,23 +3537,23 @@
       </c>
       <c r="E82" s="25" t="inlineStr">
         <is>
-          <t>练气木桩</t>
+          <t>筑基木桩</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
         <v>4008</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>10012</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="83" ht="16.5" customHeight="1" s="5">
       <c r="A83" s="3" t="n">
-        <v>100201008</v>
+        <v>100201009</v>
       </c>
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>筑基木桩</t>
+          <t>金丹木桩</t>
         </is>
       </c>
       <c r="C83" s="26" t="inlineStr">
@@ -3487,23 +3566,23 @@
       </c>
       <c r="E83" s="25" t="inlineStr">
         <is>
-          <t>筑基木桩</t>
+          <t>金丹木桩</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
         <v>4008</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="5">
       <c r="A84" s="3" t="n">
-        <v>100201009</v>
+        <v>100201010</v>
       </c>
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>金丹木桩</t>
+          <t>元婴木桩</t>
         </is>
       </c>
       <c r="C84" s="26" t="inlineStr">
@@ -3516,23 +3595,23 @@
       </c>
       <c r="E84" s="25" t="inlineStr">
         <is>
-          <t>金丹木桩</t>
+          <t>元婴木桩</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
         <v>4008</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>10014</v>
+        <v>10015</v>
       </c>
     </row>
     <row r="85" ht="16.5" customHeight="1" s="5">
       <c r="A85" s="3" t="n">
-        <v>100201010</v>
+        <v>100201011</v>
       </c>
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>元婴木桩</t>
+          <t>化神木桩</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
@@ -3545,48 +3624,48 @@
       </c>
       <c r="E85" s="25" t="inlineStr">
         <is>
-          <t>元婴木桩</t>
+          <t>化神木桩</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
         <v>4008</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>10015</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="86" ht="16.5" customHeight="1" s="5">
       <c r="A86" s="3" t="n">
-        <v>100201011</v>
-      </c>
-      <c r="B86" s="25" t="inlineStr">
-        <is>
-          <t>化神木桩</t>
+        <v>100201012</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
         </is>
       </c>
       <c r="C86" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
+          <t>WorldInteractiveObject</t>
         </is>
       </c>
       <c r="D86" s="26" t="n">
-        <v>1033</v>
-      </c>
-      <c r="E86" s="25" t="inlineStr">
-        <is>
-          <t>化神木桩</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="n">
-        <v>4008</v>
+        <v>1031</v>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>4006</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>10016</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1" s="5">
       <c r="A87" s="3" t="n">
-        <v>100201012</v>
+        <v>100201013</v>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
@@ -3610,43 +3689,43 @@
         <v>4006</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>10027</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="88" ht="16.5" customHeight="1" s="5">
       <c r="A88" s="3" t="n">
-        <v>100201013</v>
-      </c>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>低级灵脉</t>
+        <v>100201014</v>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>游荡怪物</t>
         </is>
       </c>
       <c r="C88" s="26" t="inlineStr">
         <is>
-          <t>WorldInteractiveObject</t>
+          <t>WorldNonPlayer</t>
         </is>
       </c>
       <c r="D88" s="26" t="n">
-        <v>1031</v>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>低级灵脉</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="n">
-        <v>4006</v>
+        <v>1032</v>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>游荡怪物</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>4008</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>10028</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="89" ht="16.5" customHeight="1" s="5">
       <c r="A89" s="3" t="n">
-        <v>100201014</v>
-      </c>
-      <c r="B89" s="27" t="inlineStr">
+        <v>100201015</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>游荡怪物</t>
         </is>
@@ -3657,9 +3736,9 @@
         </is>
       </c>
       <c r="D89" s="26" t="n">
-        <v>1032</v>
-      </c>
-      <c r="E89" s="27" t="inlineStr">
+        <v>1033</v>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>游荡怪物</t>
         </is>
@@ -3668,16 +3747,16 @@
         <v>4008</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>10030</v>
+        <v>10031</v>
       </c>
     </row>
     <row r="90" ht="16.5" customHeight="1" s="5">
       <c r="A90" s="3" t="n">
-        <v>100201015</v>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>游荡怪物</t>
+        <v>10013111000</v>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>获取洞府</t>
         </is>
       </c>
       <c r="C90" s="26" t="inlineStr">
@@ -3686,164 +3765,154 @@
         </is>
       </c>
       <c r="D90" s="26" t="n">
-        <v>1033</v>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>游荡怪物</t>
+        <v>1021</v>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>海洋洞府师兄</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>10031</v>
+        <v>10029</v>
       </c>
     </row>
     <row r="91" ht="16.5" customHeight="1" s="5">
       <c r="A91" s="3" t="n">
-        <v>10013111000</v>
-      </c>
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>获取洞府</t>
+        <v>10013111001</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
         </is>
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
+          <t>WorldInteractiveObject</t>
         </is>
       </c>
       <c r="D91" s="26" t="n">
-        <v>1021</v>
-      </c>
-      <c r="E91" s="27" t="inlineStr">
-        <is>
-          <t>海洋洞府师兄</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="n">
-        <v>4007</v>
+        <v>1031</v>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>4006</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>10029</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="92" ht="16.5" customHeight="1" s="5">
       <c r="A92" s="3" t="n">
-        <v>10013111001</v>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t>低级灵脉</t>
+        <v>10013111002</v>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>游荡怪物</t>
         </is>
       </c>
       <c r="C92" s="26" t="inlineStr">
         <is>
-          <t>WorldInteractiveObject</t>
+          <t>WorldNonPlayer</t>
         </is>
       </c>
       <c r="D92" s="26" t="n">
-        <v>1031</v>
-      </c>
-      <c r="E92" s="10" t="inlineStr">
-        <is>
-          <t>低级灵脉</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>4006</v>
+        <v>1032</v>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>游荡怪物</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>4008</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>10027</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="93" ht="16.5" customHeight="1" s="5">
       <c r="A93" s="3" t="n">
-        <v>10013111002</v>
-      </c>
-      <c r="B93" s="27" t="inlineStr">
-        <is>
-          <t>游荡怪物</t>
+        <v>10013112001</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
         </is>
       </c>
       <c r="C93" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
+          <t>WorldInteractiveObject</t>
         </is>
       </c>
       <c r="D93" s="26" t="n">
-        <v>1032</v>
-      </c>
-      <c r="E93" s="27" t="inlineStr">
-        <is>
-          <t>游荡怪物</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="n">
-        <v>4008</v>
+        <v>1031</v>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>低级灵脉</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>4006</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>10030</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="94" ht="16.5" customHeight="1" s="5">
       <c r="A94" s="3" t="n">
-        <v>10013112001</v>
-      </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t>低级灵脉</t>
+        <v>10013112002</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>游荡怪物</t>
         </is>
       </c>
       <c r="C94" s="26" t="inlineStr">
         <is>
-          <t>WorldInteractiveObject</t>
+          <t>WorldNonPlayer</t>
         </is>
       </c>
       <c r="D94" s="26" t="n">
-        <v>1031</v>
-      </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t>低级灵脉</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>4006</v>
+        <v>1033</v>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>游荡怪物</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>4008</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>10028</v>
+        <v>10031</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>10013112002</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>游荡怪物</t>
-        </is>
-      </c>
+        <v>10013112003</v>
+      </c>
+      <c r="B95" s="4" t="n"/>
       <c r="C95" s="26" t="inlineStr">
         <is>
-          <t>WorldNonPlayer</t>
-        </is>
-      </c>
-      <c r="D95" s="26" t="n">
-        <v>1033</v>
-      </c>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="D95" s="26" t="n"/>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>游荡怪物</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="n">
-        <v>4008</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>10031</v>
-      </c>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="n"/>
+      <c r="H95" s="12" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A10">
@@ -3962,6 +4031,7 @@
   </conditionalFormatting>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>